--- a/results/job_matches_2026-06-14.xlsx
+++ b/results/job_matches_2026-06-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Midrex Technologies Inc</t>
+          <t>Loftware</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>32.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f7fe854f6a6907</t>
+          <t>https://www.indeed.com/viewjob?jk=328900ab048cf04d</t>
         </is>
       </c>
     </row>
@@ -573,420 +573,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b4b729357fee0da</t>
+          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5860ee0655d6fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e67b07fb6f9c29</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebd82ca33ca821</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cloud Systems Engineer III</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Orange County's Credit Union</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Santa Ana, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Architect</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0905912913a35c</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5b987c1cb763e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI Architect</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19fa9727f194c93a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f89fd566c7357b0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Wichita, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0be12bfd78e5a42</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Architect</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Wichita, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa18885de990da95</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-14.xlsx
+++ b/results/job_matches_2026-06-14.xlsx
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
+          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-14.xlsx
+++ b/results/job_matches_2026-06-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,105 +503,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEVOPS ENGINEER</t>
+          <t>Senior Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>American Software Solutions INC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
+          <t>https://www.indeed.com/viewjob?jk=efb0cc4e514cfd3d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Ag &amp; Trading</t>
+          <t>DEVOPS ENGINEER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>NYC Human Resources Administration</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
+          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Sr. Data Engineer - Ag &amp; Trading</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
+          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
         </is>
       </c>
     </row>
@@ -637,6 +637,41 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cloud Systems Engineer III</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Orange County's Credit Union</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Santa Ana, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-14.xlsx
+++ b/results/job_matches_2026-06-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,138 +538,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEVOPS ENGINEER</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NYC Human Resources Administration</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, ELT, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1766fc067ea2cb5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Ag &amp; Trading</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8edb3b00b860017</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cloud Systems Engineer III</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Orange County's Credit Union</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Santa Ana, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
         </is>

--- a/results/job_matches_2026-06-14.xlsx
+++ b/results/job_matches_2026-06-14.xlsx
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
+          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-14.xlsx
+++ b/results/job_matches_2026-06-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Full Stack Python Engineer, Senior Associate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2097aeafe81a958</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc9571f04802a53b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-14.xlsx
+++ b/results/job_matches_2026-06-14.xlsx
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Full Stack Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554665f7af0eaf0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9571f04802a53b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Python Engineer, Senior Associate</t>
+          <t>Senior Solution Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9571f04802a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c823da42c3926a3</t>
         </is>
       </c>
     </row>
